--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772271</v>
+        <v>119772308</v>
       </c>
       <c r="B3" t="n">
-        <v>79635</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604137</v>
+        <v>604132</v>
       </c>
       <c r="R3" t="n">
-        <v>7064110</v>
+        <v>7064105</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772308</v>
+        <v>119772271</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>79635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604132</v>
+        <v>604137</v>
       </c>
       <c r="R4" t="n">
-        <v>7064105</v>
+        <v>7064110</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119772229</v>
+        <v>119772308</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604162</v>
+        <v>604132</v>
       </c>
       <c r="R2" t="n">
-        <v>7064090</v>
+        <v>7064105</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772308</v>
+        <v>119772515</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604132</v>
+        <v>604102</v>
       </c>
       <c r="R3" t="n">
-        <v>7064105</v>
+        <v>7064123</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772271</v>
+        <v>119772400</v>
       </c>
       <c r="B4" t="n">
-        <v>79635</v>
+        <v>91844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604137</v>
+        <v>604127</v>
       </c>
       <c r="R4" t="n">
-        <v>7064110</v>
+        <v>7064103</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119773203</v>
+        <v>119772419</v>
       </c>
       <c r="B5" t="n">
-        <v>90712</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603948</v>
+        <v>604157</v>
       </c>
       <c r="R5" t="n">
-        <v>7064267</v>
+        <v>7064107</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772400</v>
+        <v>119772313</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>79115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604127</v>
+        <v>604161</v>
       </c>
       <c r="R6" t="n">
-        <v>7064103</v>
+        <v>7064090</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119772515</v>
+        <v>119773203</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604102</v>
+        <v>603948</v>
       </c>
       <c r="R7" t="n">
-        <v>7064123</v>
+        <v>7064267</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119772313</v>
+        <v>119772611</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604161</v>
+        <v>604084</v>
       </c>
       <c r="R8" t="n">
-        <v>7064090</v>
+        <v>7064202</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119773406</v>
+        <v>119772271</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>79635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603959</v>
+        <v>604137</v>
       </c>
       <c r="R9" t="n">
-        <v>7064370</v>
+        <v>7064110</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772856</v>
+        <v>119772229</v>
       </c>
       <c r="B10" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604026</v>
+        <v>604162</v>
       </c>
       <c r="R10" t="n">
-        <v>7064222</v>
+        <v>7064090</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119773104</v>
+        <v>119773406</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603986</v>
+        <v>603959</v>
       </c>
       <c r="R11" t="n">
-        <v>7064236</v>
+        <v>7064370</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1692,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119772806</v>
+        <v>119772856</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>90712</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604020</v>
+        <v>604026</v>
       </c>
       <c r="R12" t="n">
-        <v>7064238</v>
+        <v>7064222</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,22 +1794,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119772611</v>
+        <v>119773104</v>
       </c>
       <c r="B13" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604084</v>
+        <v>603986</v>
       </c>
       <c r="R13" t="n">
-        <v>7064202</v>
+        <v>7064236</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119772419</v>
+        <v>119772806</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604157</v>
+        <v>604020</v>
       </c>
       <c r="R15" t="n">
-        <v>7064107</v>
+        <v>7064238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119773406</v>
+        <v>119772856</v>
       </c>
       <c r="B11" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603959</v>
+        <v>604026</v>
       </c>
       <c r="R11" t="n">
-        <v>7064370</v>
+        <v>7064222</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119772856</v>
+        <v>119773406</v>
       </c>
       <c r="B12" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604026</v>
+        <v>603959</v>
       </c>
       <c r="R12" t="n">
-        <v>7064222</v>
+        <v>7064370</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119772308</v>
+        <v>119773104</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604132</v>
+        <v>603986</v>
       </c>
       <c r="R2" t="n">
-        <v>7064105</v>
+        <v>7064236</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772515</v>
+        <v>119772313</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604102</v>
+        <v>604161</v>
       </c>
       <c r="R3" t="n">
-        <v>7064123</v>
+        <v>7064090</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772400</v>
+        <v>119772515</v>
       </c>
       <c r="B4" t="n">
-        <v>91844</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604127</v>
+        <v>604102</v>
       </c>
       <c r="R4" t="n">
-        <v>7064103</v>
+        <v>7064123</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119772419</v>
+        <v>119772229</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604157</v>
+        <v>604162</v>
       </c>
       <c r="R5" t="n">
-        <v>7064107</v>
+        <v>7064090</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772313</v>
+        <v>119773406</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604161</v>
+        <v>603959</v>
       </c>
       <c r="R6" t="n">
-        <v>7064090</v>
+        <v>7064370</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119773203</v>
+        <v>119772611</v>
       </c>
       <c r="B7" t="n">
-        <v>90712</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603948</v>
+        <v>604084</v>
       </c>
       <c r="R7" t="n">
-        <v>7064267</v>
+        <v>7064202</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1284,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119772611</v>
+        <v>119772737</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604084</v>
+        <v>604027</v>
       </c>
       <c r="R8" t="n">
-        <v>7064202</v>
+        <v>7064227</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772271</v>
+        <v>119772419</v>
       </c>
       <c r="B9" t="n">
-        <v>79635</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604137</v>
+        <v>604157</v>
       </c>
       <c r="R9" t="n">
-        <v>7064110</v>
+        <v>7064107</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772229</v>
+        <v>119772856</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604162</v>
+        <v>604026</v>
       </c>
       <c r="R10" t="n">
-        <v>7064090</v>
+        <v>7064222</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119772856</v>
+        <v>119772806</v>
       </c>
       <c r="B11" t="n">
-        <v>90712</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604026</v>
+        <v>604020</v>
       </c>
       <c r="R11" t="n">
-        <v>7064222</v>
+        <v>7064238</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119773406</v>
+        <v>119772400</v>
       </c>
       <c r="B12" t="n">
-        <v>78263</v>
+        <v>91844</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603959</v>
+        <v>604127</v>
       </c>
       <c r="R12" t="n">
-        <v>7064370</v>
+        <v>7064103</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119773104</v>
+        <v>119772271</v>
       </c>
       <c r="B13" t="n">
-        <v>78171</v>
+        <v>79635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603986</v>
+        <v>604137</v>
       </c>
       <c r="R13" t="n">
-        <v>7064236</v>
+        <v>7064110</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1896,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119772737</v>
+        <v>119773203</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90712</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604027</v>
+        <v>603948</v>
       </c>
       <c r="R14" t="n">
-        <v>7064227</v>
+        <v>7064267</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119772806</v>
+        <v>119772308</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,41 +2013,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604020</v>
+        <v>604132</v>
       </c>
       <c r="R15" t="n">
-        <v>7064238</v>
+        <v>7064105</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772419</v>
+        <v>119772856</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>90712</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604157</v>
+        <v>604026</v>
       </c>
       <c r="R9" t="n">
-        <v>7064107</v>
+        <v>7064222</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772856</v>
+        <v>119772419</v>
       </c>
       <c r="B10" t="n">
-        <v>90712</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604026</v>
+        <v>604157</v>
       </c>
       <c r="R10" t="n">
-        <v>7064222</v>
+        <v>7064107</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1581,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119773104</v>
+        <v>119772856</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>90712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603986</v>
+        <v>604026</v>
       </c>
       <c r="R2" t="n">
-        <v>7064236</v>
+        <v>7064222</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772313</v>
+        <v>119773406</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604161</v>
+        <v>603959</v>
       </c>
       <c r="R3" t="n">
-        <v>7064090</v>
+        <v>7064370</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772515</v>
+        <v>119772313</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604102</v>
+        <v>604161</v>
       </c>
       <c r="R4" t="n">
-        <v>7064123</v>
+        <v>7064090</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119772229</v>
+        <v>119773203</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604162</v>
+        <v>603948</v>
       </c>
       <c r="R5" t="n">
-        <v>7064090</v>
+        <v>7064267</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119773406</v>
+        <v>119772737</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603959</v>
+        <v>604027</v>
       </c>
       <c r="R6" t="n">
-        <v>7064370</v>
+        <v>7064227</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119772611</v>
+        <v>119772400</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604084</v>
+        <v>604127</v>
       </c>
       <c r="R7" t="n">
-        <v>7064202</v>
+        <v>7064103</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119772737</v>
+        <v>119772515</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604027</v>
+        <v>604102</v>
       </c>
       <c r="R8" t="n">
-        <v>7064227</v>
+        <v>7064123</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772856</v>
+        <v>119772271</v>
       </c>
       <c r="B9" t="n">
-        <v>90712</v>
+        <v>79635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604026</v>
+        <v>604137</v>
       </c>
       <c r="R9" t="n">
-        <v>7064222</v>
+        <v>7064110</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772419</v>
+        <v>119772308</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,37 +1507,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604157</v>
+        <v>604132</v>
       </c>
       <c r="R10" t="n">
-        <v>7064107</v>
+        <v>7064105</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119772806</v>
+        <v>119772611</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604020</v>
+        <v>604084</v>
       </c>
       <c r="R11" t="n">
-        <v>7064238</v>
+        <v>7064202</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119772400</v>
+        <v>119772419</v>
       </c>
       <c r="B12" t="n">
-        <v>91844</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604127</v>
+        <v>604157</v>
       </c>
       <c r="R12" t="n">
-        <v>7064103</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1794,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119772271</v>
+        <v>119773104</v>
       </c>
       <c r="B13" t="n">
-        <v>79635</v>
+        <v>78171</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604137</v>
+        <v>603986</v>
       </c>
       <c r="R13" t="n">
-        <v>7064110</v>
+        <v>7064236</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1887,22 +1896,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119773203</v>
+        <v>119772229</v>
       </c>
       <c r="B14" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603948</v>
+        <v>604162</v>
       </c>
       <c r="R14" t="n">
-        <v>7064267</v>
+        <v>7064090</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119772308</v>
+        <v>119772806</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,50 +2022,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604132</v>
+        <v>604020</v>
       </c>
       <c r="R15" t="n">
-        <v>7064105</v>
+        <v>7064238</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772271</v>
+        <v>119772308</v>
       </c>
       <c r="B9" t="n">
-        <v>79635</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604137</v>
+        <v>604132</v>
       </c>
       <c r="R9" t="n">
-        <v>7064110</v>
+        <v>7064105</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772308</v>
+        <v>119772271</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>79635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,47 +1512,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604132</v>
+        <v>604137</v>
       </c>
       <c r="R10" t="n">
-        <v>7064105</v>
+        <v>7064110</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119772856</v>
+        <v>119773406</v>
       </c>
       <c r="B2" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604026</v>
+        <v>603959</v>
       </c>
       <c r="R2" t="n">
-        <v>7064222</v>
+        <v>7064370</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119773406</v>
+        <v>119772856</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603959</v>
+        <v>604026</v>
       </c>
       <c r="R3" t="n">
-        <v>7064370</v>
+        <v>7064222</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772737</v>
+        <v>119772400</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>91844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604027</v>
+        <v>604127</v>
       </c>
       <c r="R6" t="n">
-        <v>7064227</v>
+        <v>7064103</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119772400</v>
+        <v>119772737</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604127</v>
+        <v>604027</v>
       </c>
       <c r="R7" t="n">
-        <v>7064103</v>
+        <v>7064227</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772308</v>
+        <v>119772271</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>79635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,47 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604132</v>
+        <v>604137</v>
       </c>
       <c r="R9" t="n">
-        <v>7064105</v>
+        <v>7064110</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772271</v>
+        <v>119772308</v>
       </c>
       <c r="B10" t="n">
-        <v>79635</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,38 +1503,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604137</v>
+        <v>604132</v>
       </c>
       <c r="R10" t="n">
-        <v>7064110</v>
+        <v>7064105</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119773406</v>
+        <v>119772856</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603959</v>
+        <v>604026</v>
       </c>
       <c r="R2" t="n">
-        <v>7064370</v>
+        <v>7064222</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772856</v>
+        <v>119773406</v>
       </c>
       <c r="B3" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604026</v>
+        <v>603959</v>
       </c>
       <c r="R3" t="n">
-        <v>7064222</v>
+        <v>7064370</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772400</v>
+        <v>119772737</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604127</v>
+        <v>604027</v>
       </c>
       <c r="R6" t="n">
-        <v>7064103</v>
+        <v>7064227</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119772737</v>
+        <v>119772400</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604027</v>
+        <v>604127</v>
       </c>
       <c r="R7" t="n">
-        <v>7064227</v>
+        <v>7064103</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119772856</v>
+        <v>119773406</v>
       </c>
       <c r="B2" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604026</v>
+        <v>603959</v>
       </c>
       <c r="R2" t="n">
-        <v>7064222</v>
+        <v>7064370</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119773406</v>
+        <v>119772856</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603959</v>
+        <v>604026</v>
       </c>
       <c r="R3" t="n">
-        <v>7064370</v>
+        <v>7064222</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119773406</v>
+        <v>119772419</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603959</v>
+        <v>604157</v>
       </c>
       <c r="R2" t="n">
-        <v>7064370</v>
+        <v>7064107</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772856</v>
+        <v>119772806</v>
       </c>
       <c r="B3" t="n">
-        <v>90712</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604026</v>
+        <v>604020</v>
       </c>
       <c r="R3" t="n">
-        <v>7064222</v>
+        <v>7064238</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772313</v>
+        <v>119772611</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604161</v>
+        <v>604084</v>
       </c>
       <c r="R4" t="n">
-        <v>7064090</v>
+        <v>7064202</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>119773203</v>
       </c>
       <c r="B5" t="n">
-        <v>90712</v>
+        <v>90730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772737</v>
+        <v>119772308</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604027</v>
+        <v>604132</v>
       </c>
       <c r="R6" t="n">
-        <v>7064227</v>
+        <v>7064105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1188,7 +1197,7 @@
         <v>119772400</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>91862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119772515</v>
+        <v>119772229</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604102</v>
+        <v>604162</v>
       </c>
       <c r="R8" t="n">
-        <v>7064123</v>
+        <v>7064090</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119772271</v>
+        <v>119772856</v>
       </c>
       <c r="B9" t="n">
-        <v>79635</v>
+        <v>90730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604137</v>
+        <v>604026</v>
       </c>
       <c r="R9" t="n">
-        <v>7064110</v>
+        <v>7064222</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772308</v>
+        <v>119772313</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>79131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,46 +1516,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604132</v>
+        <v>604161</v>
       </c>
       <c r="R10" t="n">
-        <v>7064105</v>
+        <v>7064090</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119772611</v>
+        <v>119772737</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604084</v>
+        <v>604027</v>
       </c>
       <c r="R11" t="n">
-        <v>7064202</v>
+        <v>7064227</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119772419</v>
+        <v>119773104</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604157</v>
+        <v>603986</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064236</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119773104</v>
+        <v>119773406</v>
       </c>
       <c r="B13" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603986</v>
+        <v>603959</v>
       </c>
       <c r="R13" t="n">
-        <v>7064236</v>
+        <v>7064370</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1896,22 +1896,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119772229</v>
+        <v>119772515</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604162</v>
+        <v>604102</v>
       </c>
       <c r="R14" t="n">
-        <v>7064090</v>
+        <v>7064123</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119772806</v>
+        <v>119772271</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>79651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604020</v>
+        <v>604137</v>
       </c>
       <c r="R15" t="n">
-        <v>7064238</v>
+        <v>7064110</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119772611</v>
+        <v>119773203</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>90730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604084</v>
+        <v>603948</v>
       </c>
       <c r="R4" t="n">
-        <v>7064202</v>
+        <v>7064267</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119773203</v>
+        <v>119772611</v>
       </c>
       <c r="B5" t="n">
-        <v>90730</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603948</v>
+        <v>604084</v>
       </c>
       <c r="R5" t="n">
-        <v>7064267</v>
+        <v>7064202</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 29247-2024 artfynd.xlsx
+++ b/artfynd/A 29247-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119772419</v>
+        <v>119772271</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>79651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604157</v>
+        <v>604137</v>
       </c>
       <c r="R2" t="n">
-        <v>7064107</v>
+        <v>7064110</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119772806</v>
+        <v>119773203</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604020</v>
+        <v>603948</v>
       </c>
       <c r="R3" t="n">
-        <v>7064238</v>
+        <v>7064267</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119773203</v>
+        <v>119772737</v>
       </c>
       <c r="B4" t="n">
-        <v>90730</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603948</v>
+        <v>604027</v>
       </c>
       <c r="R4" t="n">
-        <v>7064267</v>
+        <v>7064227</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119772611</v>
+        <v>119772515</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604084</v>
+        <v>604102</v>
       </c>
       <c r="R5" t="n">
-        <v>7064202</v>
+        <v>7064123</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119772308</v>
+        <v>119772313</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,46 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604132</v>
+        <v>604161</v>
       </c>
       <c r="R6" t="n">
-        <v>7064105</v>
+        <v>7064090</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119772400</v>
+        <v>119772308</v>
       </c>
       <c r="B7" t="n">
-        <v>91862</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1197,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mjövattenkullen, Mjövattenkullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604127</v>
+        <v>604132</v>
       </c>
       <c r="R7" t="n">
-        <v>7064103</v>
+        <v>7064105</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119772229</v>
+        <v>119772400</v>
       </c>
       <c r="B8" t="n">
-        <v>78279</v>
+        <v>91862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604162</v>
+        <v>604127</v>
       </c>
       <c r="R8" t="n">
-        <v>7064090</v>
+        <v>7064103</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119772313</v>
+        <v>119772806</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604161</v>
+        <v>604020</v>
       </c>
       <c r="R10" t="n">
-        <v>7064090</v>
+        <v>7064238</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119772737</v>
+        <v>119772611</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604027</v>
+        <v>604084</v>
       </c>
       <c r="R11" t="n">
-        <v>7064227</v>
+        <v>7064202</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119773104</v>
+        <v>119772419</v>
       </c>
       <c r="B12" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603986</v>
+        <v>604157</v>
       </c>
       <c r="R12" t="n">
-        <v>7064236</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119772515</v>
+        <v>119773104</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604102</v>
+        <v>603986</v>
       </c>
       <c r="R14" t="n">
-        <v>7064123</v>
+        <v>7064236</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1998,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119772271</v>
+        <v>119772229</v>
       </c>
       <c r="B15" t="n">
-        <v>79651</v>
+        <v>78279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604137</v>
+        <v>604162</v>
       </c>
       <c r="R15" t="n">
-        <v>7064110</v>
+        <v>7064090</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
